--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:42:29+00:00</t>
+    <t>2024-03-04T16:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="446">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T10:45:14+00:00</t>
+    <t>2024-03-07T10:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -689,6 +689,195 @@
     <t>Identifiant fonctionnel, numéro d'autorisation ARHGOS (numeroAutorisationARHGOS).</t>
   </si>
   <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.use</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.type</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.system</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>https://arhgos.ars.sante.fr/</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.value</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.period</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.assigner</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
     <t>HealthcareService.active</t>
   </si>
   <si>
@@ -730,10 +919,6 @@
     <t>This property is recommended to be the same as the Location's managingOrganization, and if not provided should be interpreted as such. If the Location does not have a managing Organization, then this property should be populated.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>.scopingRole.Organization</t>
   </si>
   <si>
@@ -744,10 +929,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>La modalité étant un mode d’application ou un type de soin prévu par les textes réglementaires encadrant chaque activité de soins (modalite).</t>
   </si>
   <si>
@@ -755,9 +936,6 @@
   </si>
   <si>
     <t>Selecting a Service Category then determines the list of relevant service types that can be selected in the primary service type.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J132-ModaliteActivite-RASS/FHIR/JDV-J132-ModaliteActivite-RASS</t>
@@ -1197,22 +1375,10 @@
     <t>HealthcareService.notAvailable.during</t>
   </si>
   <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
     <t>Service not available from this date</t>
   </si>
   <si>
     <t>Service is not available (seasonally or for a public holiday) from this date.</t>
-  </si>
-  <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>HealthcareService.availabilityExceptions</t>
@@ -1554,7 +1720,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL62"/>
+  <dimension ref="A1:AL70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.55078125" customWidth="true" bestFit="true"/>
@@ -1576,7 +1742,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
@@ -1592,7 +1758,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="72.5234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -3979,7 +4145,7 @@
         <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3996,30 +4162,26 @@
         <v>75</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>216</v>
+        <v>100</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q23" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
         <v>75</v>
       </c>
@@ -4063,7 +4225,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>215</v>
+        <v>103</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4072,56 +4234,56 @@
         <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>221</v>
+        <v>104</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>222</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>224</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>225</v>
+        <v>108</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>226</v>
+        <v>109</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>227</v>
+        <v>110</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4159,34 +4321,34 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>223</v>
+        <v>114</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>228</v>
+        <v>115</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>75</v>
@@ -4194,44 +4356,46 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I25" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>232</v>
+        <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
       </c>
@@ -4255,11 +4419,13 @@
         <v>75</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -4277,13 +4443,13 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>96</v>
@@ -4292,29 +4458,29 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>239</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>241</v>
+        <v>75</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>75</v>
@@ -4329,15 +4495,17 @@
         <v>232</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
       </c>
@@ -4361,11 +4529,13 @@
         <v>75</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>75</v>
@@ -4383,13 +4553,13 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>96</v>
@@ -4398,7 +4568,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>75</v>
@@ -4406,10 +4576,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4417,13 +4587,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>75</v>
@@ -4432,18 +4602,20 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>232</v>
+        <v>133</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
       </c>
@@ -4452,10 +4624,10 @@
         <v>75</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>75</v>
+        <v>246</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>75</v>
+        <v>247</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>75</v>
@@ -4467,11 +4639,13 @@
         <v>75</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>75</v>
@@ -4489,13 +4663,13 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>96</v>
@@ -4504,7 +4678,7 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>75</v>
@@ -4512,7 +4686,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>251</v>
@@ -4526,7 +4700,7 @@
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>75</v>
@@ -4538,16 +4712,16 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4561,7 +4735,7 @@
         <v>75</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>75</v>
+        <v>255</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>75</v>
@@ -4597,25 +4771,25 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>228</v>
+        <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>257</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -4623,7 +4797,7 @@
         <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4646,16 +4820,16 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>100</v>
+        <v>260</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4705,7 +4879,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4717,10 +4891,10 @@
         <v>96</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>265</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>75</v>
@@ -4728,10 +4902,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4754,16 +4928,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>100</v>
+        <v>269</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4813,7 +4987,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4825,10 +4999,10 @@
         <v>96</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>274</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>75</v>
@@ -4836,10 +5010,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4856,28 +5030,30 @@
         <v>75</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q31" s="2"/>
+      <c r="Q31" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="R31" t="s" s="2">
         <v>75</v>
       </c>
@@ -4921,7 +5097,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4936,18 +5112,18 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>75</v>
+        <v>283</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4961,7 +5137,7 @@
         <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>75</v>
@@ -4970,16 +5146,16 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5029,7 +5205,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5041,10 +5217,10 @@
         <v>96</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>75</v>
@@ -5052,14 +5228,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5069,25 +5245,25 @@
         <v>77</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>282</v>
+        <v>232</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5113,13 +5289,11 @@
         <v>75</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>75</v>
+        <v>295</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>75</v>
@@ -5137,7 +5311,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5149,25 +5323,25 @@
         <v>96</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>286</v>
+        <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>75</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>75</v>
+        <v>299</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5183,19 +5357,19 @@
         <v>75</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5221,13 +5395,11 @@
         <v>75</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>75</v>
+        <v>303</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5245,7 +5417,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5257,10 +5429,10 @@
         <v>96</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>228</v>
+        <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>75</v>
@@ -5268,10 +5440,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5285,25 +5457,25 @@
         <v>77</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>232</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5329,13 +5501,11 @@
         <v>75</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5353,7 +5523,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5368,7 +5538,7 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>75</v>
@@ -5376,10 +5546,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5399,18 +5569,20 @@
         <v>75</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -5459,7 +5631,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5471,21 +5643,21 @@
         <v>96</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>274</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>75</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5505,18 +5677,20 @@
         <v>75</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>100</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>101</v>
+        <v>317</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -5565,7 +5739,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>103</v>
+        <v>316</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5574,13 +5748,13 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>104</v>
+        <v>320</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>75</v>
@@ -5588,21 +5762,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>75</v>
@@ -5611,19 +5785,19 @@
         <v>75</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>108</v>
+        <v>322</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>109</v>
+        <v>323</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>110</v>
+        <v>324</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5661,34 +5835,34 @@
         <v>75</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>114</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>98</v>
+        <v>325</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>75</v>
@@ -5696,46 +5870,44 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>306</v>
+        <v>75</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
       </c>
@@ -5783,22 +5955,22 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>98</v>
+        <v>331</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>75</v>
@@ -5806,10 +5978,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5829,19 +6001,19 @@
         <v>75</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>232</v>
+        <v>333</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>244</v>
+        <v>336</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5867,10 +6039,10 @@
         <v>75</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>313</v>
+        <v>75</v>
       </c>
       <c r="Z40" t="s" s="2">
         <v>75</v>
@@ -5891,7 +6063,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5903,10 +6075,10 @@
         <v>96</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>337</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>75</v>
@@ -5914,10 +6086,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5928,7 +6100,7 @@
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>75</v>
@@ -5940,16 +6112,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>269</v>
+        <v>340</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5999,22 +6171,22 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>97</v>
+        <v>344</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>318</v>
+        <v>345</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>75</v>
@@ -6022,10 +6194,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6048,16 +6220,16 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>232</v>
+        <v>310</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6083,13 +6255,13 @@
         <v>75</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>323</v>
+        <v>75</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>324</v>
+        <v>75</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>75</v>
@@ -6107,7 +6279,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6119,10 +6291,10 @@
         <v>96</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>97</v>
+        <v>274</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>75</v>
@@ -6130,10 +6302,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6147,7 +6319,7 @@
         <v>77</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>75</v>
@@ -6159,13 +6331,13 @@
         <v>232</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6191,11 +6363,13 @@
         <v>75</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -6213,7 +6387,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6228,7 +6402,7 @@
         <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
@@ -6236,10 +6410,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6262,17 +6436,15 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>232</v>
+        <v>358</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6297,13 +6469,13 @@
         <v>75</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>174</v>
+        <v>75</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -6321,7 +6493,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6336,7 +6508,7 @@
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>335</v>
+        <v>104</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -6344,10 +6516,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6358,7 +6530,7 @@
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
@@ -6370,17 +6542,15 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>232</v>
+        <v>100</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>337</v>
+        <v>101</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>75</v>
@@ -6405,13 +6575,13 @@
         <v>75</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>339</v>
+        <v>75</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>340</v>
+        <v>75</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>75</v>
@@ -6429,22 +6599,22 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>103</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>325</v>
+        <v>104</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
@@ -6452,21 +6622,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>75</v>
@@ -6478,15 +6648,17 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>216</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>342</v>
+        <v>108</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -6523,34 +6695,34 @@
         <v>75</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>341</v>
+        <v>114</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>325</v>
+        <v>98</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
@@ -6558,14 +6730,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>75</v>
+        <v>364</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6578,24 +6750,26 @@
         <v>75</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>300</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>75</v>
       </c>
@@ -6643,7 +6817,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6655,10 +6829,10 @@
         <v>96</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>348</v>
+        <v>98</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>75</v>
@@ -6666,10 +6840,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6692,15 +6866,17 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>100</v>
+        <v>232</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>101</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -6725,10 +6901,10 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>75</v>
+        <v>371</v>
       </c>
       <c r="Z48" t="s" s="2">
         <v>75</v>
@@ -6749,7 +6925,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>103</v>
+        <v>368</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6758,13 +6934,13 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>104</v>
+        <v>356</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
@@ -6772,21 +6948,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>75</v>
@@ -6798,16 +6974,16 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>108</v>
+        <v>373</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>109</v>
+        <v>374</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>110</v>
+        <v>375</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6845,34 +7021,34 @@
         <v>75</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>114</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>98</v>
+        <v>376</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>75</v>
@@ -6880,14 +7056,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>306</v>
+        <v>75</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6900,26 +7076,24 @@
         <v>75</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>107</v>
+        <v>232</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>307</v>
+        <v>378</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>308</v>
+        <v>379</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
       </c>
@@ -6943,13 +7117,13 @@
         <v>75</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>75</v>
+        <v>381</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>75</v>
+        <v>382</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -6967,7 +7141,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>309</v>
+        <v>377</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6979,10 +7153,10 @@
         <v>96</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>98</v>
+        <v>383</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>75</v>
@@ -6990,10 +7164,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7007,7 +7181,7 @@
         <v>77</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>75</v>
@@ -7016,16 +7190,16 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>168</v>
+        <v>232</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>354</v>
+        <v>386</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>261</v>
+        <v>387</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7051,13 +7225,11 @@
         <v>75</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -7075,7 +7247,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7090,7 +7262,7 @@
         <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>75</v>
@@ -7098,10 +7270,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7112,7 +7284,7 @@
         <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>75</v>
@@ -7124,15 +7296,17 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -7157,13 +7331,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>75</v>
+        <v>174</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7181,13 +7355,13 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>96</v>
@@ -7196,7 +7370,7 @@
         <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>348</v>
+        <v>393</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>75</v>
@@ -7204,10 +7378,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7218,7 +7392,7 @@
         <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>75</v>
@@ -7230,16 +7404,16 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>361</v>
+        <v>232</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>362</v>
+        <v>395</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>364</v>
+        <v>302</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7265,13 +7439,13 @@
         <v>75</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>75</v>
+        <v>397</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>75</v>
+        <v>398</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -7289,13 +7463,13 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>96</v>
@@ -7304,7 +7478,7 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>75</v>
@@ -7312,10 +7486,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7338,17 +7512,15 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>361</v>
+        <v>277</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -7397,7 +7569,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7412,7 +7584,7 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>75</v>
@@ -7420,10 +7592,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7446,15 +7618,17 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>300</v>
+        <v>358</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -7503,7 +7677,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7518,7 +7692,7 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>348</v>
+        <v>406</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>75</v>
@@ -7526,10 +7700,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>371</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>371</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7632,10 +7806,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7740,14 +7914,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>306</v>
+        <v>364</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7769,10 +7943,10 @@
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>307</v>
+        <v>365</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>308</v>
+        <v>366</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>110</v>
@@ -7827,7 +8001,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>309</v>
+        <v>367</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7850,10 +8024,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7861,10 +8035,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>75</v>
@@ -7876,16 +8050,16 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>261</v>
+        <v>319</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7911,13 +8085,13 @@
         <v>75</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>75</v>
+        <v>413</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>75</v>
+        <v>414</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -7935,13 +8109,13 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>96</v>
@@ -7950,7 +8124,7 @@
         <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>104</v>
+        <v>406</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>75</v>
@@ -7958,10 +8132,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7984,17 +8158,15 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>378</v>
+        <v>277</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>75</v>
@@ -8043,7 +8215,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8055,10 +8227,10 @@
         <v>96</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>382</v>
+        <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>348</v>
+        <v>406</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>75</v>
@@ -8066,10 +8238,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>383</v>
+        <v>418</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>383</v>
+        <v>418</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8092,16 +8264,16 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>100</v>
+        <v>419</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>261</v>
+        <v>422</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8151,7 +8323,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>383</v>
+        <v>418</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8166,7 +8338,7 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>348</v>
+        <v>406</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8174,10 +8346,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>386</v>
+        <v>423</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>386</v>
+        <v>423</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8188,7 +8360,7 @@
         <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>75</v>
@@ -8200,16 +8372,16 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>387</v>
+        <v>419</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>255</v>
+        <v>422</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8259,29 +8431,891 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>386</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>228</v>
+        <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AL70" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL62">
+  <autoFilter ref="A1:AL70">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8291,7 +9325,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -686,7 +686,7 @@
     <t>numAutorisationArhgos</t>
   </si>
   <si>
-    <t>Identifiant fonctionnel, numéro d'autorisation ARHGOS (numeroAutorisationARHGOS).</t>
+    <t>Identifiant fonctionnel, numéro d'autorisation ARHGOS (numeroAutorisationARHGOS). Le system est mis à titre indicatif et pourra évoluer.</t>
   </si>
   <si>
     <t>HealthcareService.identifier:numAutorisationArhgos.id</t>
@@ -783,7 +783,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://arhgos.ars.sante.fr/</t>
+    <t>https://arhgos.ars.sante.fr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="434">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:53:48+00:00</t>
+    <t>2024-04-09T07:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>act[classCode=ACT][moodCode=DEF]</t>
@@ -310,334 +310,334 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace</t>
+  </si>
+  <si>
+    <t>as-ext-data-trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
+</t>
+  </si>
+  <si>
+    <t>DataTrace : Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI).</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>HealthcareService.implicitRules</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>HealthcareService.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>HealthcareService.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>HealthcareService.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-healthcareservice-authorization</t>
+  </si>
+  <si>
+    <t>as-ext-healthcareservice-authorization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization}
+</t>
+  </si>
+  <si>
+    <t>AS HealthcareService Autorization Extension</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les autorisations  des activités sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels lourds autorisés.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.extension:as-ext-data-trace</t>
-  </si>
-  <si>
-    <t>as-ext-data-trace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
-</t>
-  </si>
-  <si>
-    <t>DataTrace : Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI).</t>
-  </si>
-  <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>HealthcareService.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>HealthcareService.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>HealthcareService.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>HealthcareService.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization</t>
-  </si>
-  <si>
-    <t>as-ext-healthcareservice-authorization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization}
-</t>
-  </si>
-  <si>
-    <t>AS HealthcareService Autorization Extension</t>
-  </si>
-  <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les autorisations  des activités sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels lourds autorisés.</t>
-  </si>
-  <si>
     <t>HealthcareService.modifierExtension</t>
   </si>
   <si>
@@ -686,7 +686,7 @@
     <t>numAutorisationArhgos</t>
   </si>
   <si>
-    <t>Identifiant fonctionnel, numéro d'autorisation ARHGOS (numeroAutorisationARHGOS). Le system est mis à titre indicatif et pourra évoluer.</t>
+    <t>Identifiant fonctionnel, numéro d'autorisation ARHGOS (numeroAutorisationARHGOS).</t>
   </si>
   <si>
     <t>HealthcareService.identifier:numAutorisationArhgos.id</t>
@@ -835,15 +835,7 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
     <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
@@ -871,10 +863,6 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
   </si>
   <si>
@@ -959,9 +947,6 @@
   </si>
   <si>
     <t>The specific type of service that may be delivered or performed.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J131-CategorieActiviteSanitaireRegulee-RASS/FHIR/JDV-J131-CategorieActiviteSanitaireRegulee-RASS</t>
@@ -997,9 +982,6 @@
     <t>The location(s) where this healthcare service may be provided.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>.location.role[classCode=SDLOC]</t>
   </si>
   <si>
@@ -1013,9 +995,6 @@
   </si>
   <si>
     <t>Further description of the service as it would be presented to a consumer while searching.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>.name</t>
@@ -1049,9 +1028,6 @@
     <t>Extra details about the service that can't be placed in the other fields.</t>
   </si>
   <si>
-    <t>Systems are not required to have markdown support, so the text should be readable without markdown processing. The markdown syntax is GFM - see https://github.github.com/gfm/</t>
-  </si>
-  <si>
     <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].text</t>
   </si>
   <si>
@@ -1068,13 +1044,6 @@
     <t>If there is a photo/symbol associated with this HealthcareService, it may be included here to facilitate quick identification of the service in a list.</t>
   </si>
   <si>
-    <t>When providing a summary view (for example with Observation.value[x]) Attachment should be represented with a brief display text such as "Signed Procedure Consent".</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}</t>
-  </si>
-  <si>
     <t>.actrelationship[typeCode=SBJ].observation.value</t>
   </si>
   <si>
@@ -1094,10 +1063,6 @@
     <t>If this is empty, then refer to the location's contacts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
-  </si>
-  <si>
     <t>.telecom</t>
   </si>
   <si>
@@ -1245,9 +1210,6 @@
     <t>When using this property it indicates that the service is available with this language, it is not derived from the practitioners, and not all are required to use this language, just that this language is available while scheduling.</t>
   </si>
   <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>HealthcareService.referralMethod</t>
   </si>
   <si>
@@ -1401,9 +1363,6 @@
   </si>
   <si>
     <t>Technical endpoints providing access to services operated for the specific healthcare services defined at this resource.</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
 </sst>
 </file>
@@ -2186,13 +2145,13 @@
         <v>84</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK4" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>75</v>
@@ -2200,10 +2159,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2226,13 +2185,13 @@
         <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L5" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2283,7 +2242,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -2298,7 +2257,7 @@
         <v>75</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>75</v>
@@ -2306,14 +2265,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2332,16 +2291,16 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2379,19 +2338,19 @@
         <v>75</v>
       </c>
       <c r="AB6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC6" t="s" s="2">
+      <c r="AF6" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -2400,13 +2359,13 @@
         <v>77</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>75</v>
@@ -2414,13 +2373,13 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>75</v>
@@ -2442,13 +2401,13 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2499,7 +2458,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -2508,10 +2467,10 @@
         <v>77</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
@@ -2522,10 +2481,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2551,13 +2510,13 @@
         <v>86</v>
       </c>
       <c r="L8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2607,7 +2566,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2616,13 +2575,13 @@
         <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ8" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK8" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>75</v>
@@ -2630,10 +2589,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2656,16 +2615,16 @@
         <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2715,7 +2674,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2724,13 +2683,13 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ9" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK9" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>75</v>
@@ -2738,10 +2697,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2764,16 +2723,16 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2823,7 +2782,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2832,13 +2791,13 @@
         <v>84</v>
       </c>
       <c r="AI10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ10" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK10" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>75</v>
@@ -2846,10 +2805,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2872,16 +2831,16 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2931,7 +2890,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -2940,13 +2899,13 @@
         <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK11" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>75</v>
@@ -2954,10 +2913,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2980,16 +2939,16 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3015,31 +2974,31 @@
         <v>75</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="Z12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="AA12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3048,13 +3007,13 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK12" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>75</v>
@@ -3062,10 +3021,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3088,16 +3047,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3123,31 +3082,31 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3156,13 +3115,13 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK13" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>75</v>
@@ -3170,10 +3129,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3196,16 +3155,16 @@
         <v>85</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3255,7 +3214,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3264,13 +3223,13 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK14" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>75</v>
@@ -3278,10 +3237,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3304,16 +3263,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3339,31 +3298,31 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3372,13 +3331,13 @@
         <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK15" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>75</v>
@@ -3386,14 +3345,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3412,16 +3371,16 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3471,7 +3430,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3480,13 +3439,13 @@
         <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK16" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>75</v>
@@ -3494,14 +3453,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3520,16 +3479,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3579,7 +3538,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3594,7 +3553,7 @@
         <v>75</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>75</v>
@@ -3602,14 +3561,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3628,17 +3587,15 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>108</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3675,19 +3632,17 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC18" s="2"/>
+      <c r="AD18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC18" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>113</v>
-      </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3696,13 +3651,13 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>75</v>
@@ -3710,13 +3665,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>75</v>
@@ -3738,13 +3693,13 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3795,7 +3750,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3804,10 +3759,10 @@
         <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>75</v>
@@ -3825,7 +3780,7 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3844,7 +3799,7 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>200</v>
@@ -3853,7 +3808,7 @@
         <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O20" t="s" s="2">
         <v>202</v>
@@ -3893,16 +3848,16 @@
         <v>75</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>203</v>
@@ -3914,13 +3869,13 @@
         <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>75</v>
@@ -4008,7 +3963,7 @@
         <v>75</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>204</v>
@@ -4020,10 +3975,10 @@
         <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>210</v>
@@ -4128,10 +4083,10 @@
         <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>210</v>
@@ -4168,13 +4123,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4225,7 +4180,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4240,7 +4195,7 @@
         <v>75</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>75</v>
@@ -4255,7 +4210,7 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4274,16 +4229,16 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4321,19 +4276,19 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE24" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC24" t="s" s="2">
+      <c r="AF24" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4342,13 +4297,13 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>75</v>
@@ -4382,7 +4337,7 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>221</v>
@@ -4452,10 +4407,10 @@
         <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>229</v>
@@ -4529,7 +4484,7 @@
         <v>75</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Y26" t="s" s="2">
         <v>237</v>
@@ -4562,10 +4517,10 @@
         <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>229</v>
@@ -4602,7 +4557,7 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>242</v>
@@ -4672,10 +4627,10 @@
         <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>249</v>
@@ -4712,7 +4667,7 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>252</v>
@@ -4780,10 +4735,10 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>257</v>
@@ -4828,9 +4783,7 @@
       <c r="M29" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>263</v>
-      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -4879,7 +4832,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4888,13 +4841,13 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>265</v>
-      </c>
       <c r="AK29" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>75</v>
@@ -4902,10 +4855,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4928,16 +4881,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4987,7 +4940,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4996,13 +4949,13 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ30" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AK30" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>75</v>
@@ -5010,10 +4963,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5036,23 +4989,23 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q31" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="R31" t="s" s="2">
         <v>75</v>
@@ -5097,7 +5050,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5106,24 +5059,24 @@
         <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ31" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK31" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5146,16 +5099,16 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5205,7 +5158,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5214,13 +5167,13 @@
         <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ32" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AK32" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>75</v>
@@ -5228,14 +5181,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5257,13 +5210,13 @@
         <v>232</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5293,7 +5246,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>75</v>
@@ -5311,7 +5264,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5320,28 +5273,28 @@
         <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ33" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK33" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5363,14 +5316,12 @@
         <v>232</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5399,7 +5350,7 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5417,7 +5368,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5426,13 +5377,13 @@
         <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK34" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>75</v>
@@ -5440,10 +5391,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5469,14 +5420,12 @@
         <v>232</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5505,7 +5454,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5523,7 +5472,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5532,13 +5481,13 @@
         <v>77</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK35" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>75</v>
@@ -5546,10 +5495,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5572,17 +5521,15 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -5631,7 +5578,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5640,24 +5587,24 @@
         <v>77</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AK36" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5680,17 +5627,15 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -5739,7 +5684,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5748,13 +5693,13 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK37" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>75</v>
@@ -5762,10 +5707,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5788,16 +5733,16 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5847,7 +5792,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5856,13 +5801,13 @@
         <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ38" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK38" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>75</v>
@@ -5870,10 +5815,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5896,17 +5841,15 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -5955,7 +5898,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5964,13 +5907,13 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ39" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK39" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>75</v>
@@ -5978,10 +5921,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6004,17 +5947,15 @@
         <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -6063,7 +6004,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6072,13 +6013,13 @@
         <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ40" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="AK40" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>75</v>
@@ -6086,10 +6027,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6112,16 +6053,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6171,7 +6112,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6180,13 +6121,13 @@
         <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ41" t="s" s="2">
-        <v>344</v>
-      </c>
       <c r="AK41" t="s" s="2">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>75</v>
@@ -6194,10 +6135,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6220,16 +6161,16 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6279,7 +6220,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6288,13 +6229,13 @@
         <v>77</v>
       </c>
       <c r="AI42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ42" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AK42" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>75</v>
@@ -6302,10 +6243,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6331,13 +6272,13 @@
         <v>232</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6363,13 +6304,13 @@
         <v>75</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -6387,7 +6328,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6396,13 +6337,13 @@
         <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ43" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK43" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
@@ -6410,10 +6351,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6436,13 +6377,13 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6493,7 +6434,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6502,13 +6443,13 @@
         <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ44" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK44" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -6516,10 +6457,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6542,13 +6483,13 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6599,7 +6540,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6614,7 +6555,7 @@
         <v>75</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
@@ -6622,14 +6563,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6648,16 +6589,16 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6695,19 +6636,19 @@
         <v>75</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6716,13 +6657,13 @@
         <v>77</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
@@ -6730,14 +6671,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6756,16 +6697,16 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>202</v>
@@ -6817,7 +6758,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6826,13 +6767,13 @@
         <v>77</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>75</v>
@@ -6840,10 +6781,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6869,14 +6810,12 @@
         <v>232</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -6901,10 +6840,10 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="Z48" t="s" s="2">
         <v>75</v>
@@ -6925,7 +6864,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6934,13 +6873,13 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ48" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK48" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
@@ -6948,10 +6887,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6974,16 +6913,16 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7033,7 +6972,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7042,13 +6981,13 @@
         <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ49" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK49" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>75</v>
@@ -7056,10 +6995,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7085,13 +7024,13 @@
         <v>232</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7117,13 +7056,13 @@
         <v>75</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -7141,7 +7080,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7150,13 +7089,13 @@
         <v>77</v>
       </c>
       <c r="AI50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ50" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK50" t="s" s="2">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>75</v>
@@ -7164,10 +7103,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7193,13 +7132,13 @@
         <v>232</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7229,7 +7168,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -7247,7 +7186,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7256,13 +7195,13 @@
         <v>77</v>
       </c>
       <c r="AI51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ51" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK51" t="s" s="2">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>75</v>
@@ -7270,10 +7209,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7299,13 +7238,13 @@
         <v>232</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7331,13 +7270,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7355,7 +7294,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7364,13 +7303,13 @@
         <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ52" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK52" t="s" s="2">
-        <v>393</v>
+        <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>75</v>
@@ -7378,10 +7317,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7407,14 +7346,12 @@
         <v>232</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>75</v>
@@ -7439,13 +7376,13 @@
         <v>75</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -7463,7 +7400,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7472,13 +7409,13 @@
         <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ53" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK53" t="s" s="2">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>75</v>
@@ -7486,10 +7423,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7512,13 +7449,13 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7569,7 +7506,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7578,13 +7515,13 @@
         <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ54" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK54" t="s" s="2">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>75</v>
@@ -7592,10 +7529,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7618,16 +7555,16 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7677,7 +7614,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7686,13 +7623,13 @@
         <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ55" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK55" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>75</v>
@@ -7700,10 +7637,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7726,13 +7663,13 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7783,7 +7720,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7798,7 +7735,7 @@
         <v>75</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>75</v>
@@ -7806,14 +7743,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7832,16 +7769,16 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7879,19 +7816,19 @@
         <v>75</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7900,13 +7837,13 @@
         <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>75</v>
@@ -7914,14 +7851,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7940,16 +7877,16 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>202</v>
@@ -8001,7 +7938,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8010,13 +7947,13 @@
         <v>77</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>75</v>
@@ -8024,10 +7961,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8050,17 +7987,15 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>75</v>
@@ -8088,10 +8023,10 @@
         <v>225</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -8109,7 +8044,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8118,13 +8053,13 @@
         <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ59" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK59" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>75</v>
@@ -8132,10 +8067,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8158,13 +8093,13 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8215,7 +8150,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8224,13 +8159,13 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ60" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK60" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>75</v>
@@ -8238,10 +8173,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8264,16 +8199,16 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8323,7 +8258,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8332,13 +8267,13 @@
         <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ61" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK61" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8346,10 +8281,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8372,16 +8307,16 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8431,7 +8366,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8440,13 +8375,13 @@
         <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ62" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK62" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>75</v>
@@ -8454,10 +8389,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8480,13 +8415,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8537,7 +8472,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8546,13 +8481,13 @@
         <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ63" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK63" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>75</v>
@@ -8560,10 +8495,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8586,13 +8521,13 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8643,7 +8578,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8658,7 +8593,7 @@
         <v>75</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>75</v>
@@ -8666,14 +8601,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8692,16 +8627,16 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8739,19 +8674,19 @@
         <v>75</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8760,13 +8695,13 @@
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>75</v>
@@ -8774,14 +8709,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -8800,16 +8735,16 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>202</v>
@@ -8861,7 +8796,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -8870,13 +8805,13 @@
         <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>75</v>
@@ -8884,10 +8819,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8910,17 +8845,15 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>75</v>
@@ -8969,7 +8902,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>84</v>
@@ -8978,13 +8911,13 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ67" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK67" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>75</v>
@@ -8992,10 +8925,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9021,14 +8954,12 @@
         <v>260</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>75</v>
@@ -9077,7 +9008,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9086,13 +9017,13 @@
         <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ68" t="s" s="2">
-        <v>265</v>
-      </c>
       <c r="AK68" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>75</v>
@@ -9100,10 +9031,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9126,17 +9057,15 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -9185,7 +9114,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9194,13 +9123,13 @@
         <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ69" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK69" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>75</v>
@@ -9208,10 +9137,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9234,17 +9163,15 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -9293,7 +9220,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9302,13 +9229,13 @@
         <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ70" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AK70" t="s" s="2">
-        <v>445</v>
+        <v>102</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="446">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>act[classCode=ACT][moodCode=DEF]</t>
@@ -310,10 +310,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>HealthcareService.meta.id</t>
   </si>
   <si>
@@ -487,6 +494,9 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>HealthcareService.meta.tag</t>
   </si>
   <si>
@@ -603,16 +613,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>HealthcareService.extension</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -634,10 +638,6 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les autorisations  des activités sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels lourds autorisés.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>HealthcareService.modifierExtension</t>
   </si>
   <si>
@@ -835,7 +835,15 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
     <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
@@ -863,6 +871,10 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
   </si>
   <si>
@@ -947,6 +959,9 @@
   </si>
   <si>
     <t>The specific type of service that may be delivered or performed.</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J131-CategorieActiviteSanitaireRegulee-RASS/FHIR/JDV-J131-CategorieActiviteSanitaireRegulee-RASS</t>
@@ -982,6 +997,9 @@
     <t>The location(s) where this healthcare service may be provided.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>.location.role[classCode=SDLOC]</t>
   </si>
   <si>
@@ -995,6 +1013,9 @@
   </si>
   <si>
     <t>Further description of the service as it would be presented to a consumer while searching.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>.name</t>
@@ -1028,6 +1049,9 @@
     <t>Extra details about the service that can't be placed in the other fields.</t>
   </si>
   <si>
+    <t>Systems are not required to have markdown support, so the text should be readable without markdown processing. The markdown syntax is GFM - see https://github.github.com/gfm/</t>
+  </si>
+  <si>
     <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].text</t>
   </si>
   <si>
@@ -1044,6 +1068,13 @@
     <t>If there is a photo/symbol associated with this HealthcareService, it may be included here to facilitate quick identification of the service in a list.</t>
   </si>
   <si>
+    <t>When providing a summary view (for example with Observation.value[x]) Attachment should be represented with a brief display text such as "Signed Procedure Consent".</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}</t>
+  </si>
+  <si>
     <t>.actrelationship[typeCode=SBJ].observation.value</t>
   </si>
   <si>
@@ -1063,6 +1094,10 @@
     <t>If this is empty, then refer to the location's contacts.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
+  </si>
+  <si>
     <t>.telecom</t>
   </si>
   <si>
@@ -1210,6 +1245,9 @@
     <t>When using this property it indicates that the service is available with this language, it is not derived from the practitioners, and not all are required to use this language, just that this language is available while scheduling.</t>
   </si>
   <si>
+    <t>CD</t>
+  </si>
+  <si>
     <t>HealthcareService.referralMethod</t>
   </si>
   <si>
@@ -1363,6 +1401,9 @@
   </si>
   <si>
     <t>Technical endpoints providing access to services operated for the specific healthcare services defined at this resource.</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
 </sst>
 </file>
@@ -2145,13 +2186,13 @@
         <v>84</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>75</v>
@@ -2159,10 +2200,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2185,13 +2226,13 @@
         <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2242,7 +2283,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -2257,7 +2298,7 @@
         <v>75</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>75</v>
@@ -2265,14 +2306,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2291,16 +2332,16 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2338,19 +2379,19 @@
         <v>75</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -2359,13 +2400,13 @@
         <v>77</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>75</v>
@@ -2373,13 +2414,13 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>75</v>
@@ -2401,13 +2442,13 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2458,7 +2499,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -2467,10 +2508,10 @@
         <v>77</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
@@ -2481,10 +2522,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2510,13 +2551,13 @@
         <v>86</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2566,7 +2607,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2575,13 +2616,13 @@
         <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>75</v>
@@ -2589,10 +2630,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2615,16 +2656,16 @@
         <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2674,7 +2715,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2683,13 +2724,13 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>75</v>
@@ -2697,10 +2738,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2723,16 +2764,16 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2782,7 +2823,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2791,13 +2832,13 @@
         <v>84</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>75</v>
@@ -2805,10 +2846,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2831,16 +2872,16 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2890,7 +2931,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -2899,13 +2940,13 @@
         <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>75</v>
@@ -2913,10 +2954,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2939,16 +2980,16 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2974,13 +3015,13 @@
         <v>75</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>75</v>
@@ -2998,7 +3039,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3007,13 +3048,13 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>75</v>
@@ -3021,10 +3062,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3047,16 +3088,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3082,13 +3123,13 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>75</v>
@@ -3106,7 +3147,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3115,13 +3156,13 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>75</v>
@@ -3129,10 +3170,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3155,16 +3196,16 @@
         <v>85</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3214,7 +3255,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3223,13 +3264,13 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>75</v>
@@ -3237,10 +3278,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3263,16 +3304,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3298,13 +3339,13 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>75</v>
@@ -3322,7 +3363,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3331,13 +3372,13 @@
         <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>75</v>
@@ -3345,14 +3386,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3371,16 +3412,16 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3430,7 +3471,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3439,13 +3480,13 @@
         <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>75</v>
@@ -3453,14 +3494,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3479,16 +3520,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3538,7 +3579,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3553,7 +3594,7 @@
         <v>75</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>75</v>
@@ -3561,14 +3602,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3587,15 +3628,17 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>108</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3632,17 +3675,19 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AC18" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3651,13 +3696,13 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>75</v>
@@ -3665,13 +3710,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>75</v>
@@ -3693,13 +3738,13 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3750,7 +3795,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3759,10 +3804,10 @@
         <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>75</v>
@@ -3780,7 +3825,7 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3799,7 +3844,7 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>200</v>
@@ -3808,7 +3853,7 @@
         <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O20" t="s" s="2">
         <v>202</v>
@@ -3848,16 +3893,16 @@
         <v>75</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>203</v>
@@ -3869,13 +3914,13 @@
         <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>75</v>
@@ -3963,7 +4008,7 @@
         <v>75</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>204</v>
@@ -3975,10 +4020,10 @@
         <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>210</v>
@@ -4083,10 +4128,10 @@
         <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>210</v>
@@ -4123,13 +4168,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4180,7 +4225,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4195,7 +4240,7 @@
         <v>75</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>75</v>
@@ -4210,7 +4255,7 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4229,16 +4274,16 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4276,19 +4321,19 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4297,13 +4342,13 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>75</v>
@@ -4337,7 +4382,7 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>221</v>
@@ -4407,10 +4452,10 @@
         <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>229</v>
@@ -4484,7 +4529,7 @@
         <v>75</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y26" t="s" s="2">
         <v>237</v>
@@ -4517,10 +4562,10 @@
         <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>229</v>
@@ -4557,7 +4602,7 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>242</v>
@@ -4627,10 +4672,10 @@
         <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>249</v>
@@ -4667,7 +4712,7 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>252</v>
@@ -4735,10 +4780,10 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>257</v>
@@ -4783,7 +4828,9 @@
       <c r="M29" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="N29" s="2"/>
+      <c r="N29" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -4832,7 +4879,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4841,13 +4888,13 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>96</v>
+        <v>265</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>75</v>
@@ -4855,10 +4902,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4881,16 +4928,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4940,7 +4987,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4949,13 +4996,13 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>75</v>
@@ -4963,10 +5010,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4989,23 +5036,23 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q31" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="R31" t="s" s="2">
         <v>75</v>
@@ -5050,7 +5097,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5059,24 +5106,24 @@
         <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5099,16 +5146,16 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5158,7 +5205,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5167,13 +5214,13 @@
         <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>75</v>
@@ -5181,14 +5228,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5210,13 +5257,13 @@
         <v>232</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5246,7 +5293,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>75</v>
@@ -5264,7 +5311,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5273,28 +5320,28 @@
         <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5316,12 +5363,14 @@
         <v>232</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5350,7 +5399,7 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5368,7 +5417,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5377,13 +5426,13 @@
         <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>75</v>
@@ -5391,10 +5440,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5420,12 +5469,14 @@
         <v>232</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5454,7 +5505,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5472,7 +5523,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5481,13 +5532,13 @@
         <v>77</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>75</v>
@@ -5495,10 +5546,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5521,15 +5572,17 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -5578,7 +5631,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5587,24 +5640,24 @@
         <v>77</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5627,15 +5680,17 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -5684,7 +5739,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5693,13 +5748,13 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>75</v>
@@ -5707,10 +5762,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5733,16 +5788,16 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5792,7 +5847,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5801,13 +5856,13 @@
         <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>75</v>
@@ -5815,10 +5870,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5841,15 +5896,17 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -5898,7 +5955,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5907,13 +5964,13 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>75</v>
@@ -5921,10 +5978,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5947,15 +6004,17 @@
         <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -6004,7 +6063,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6013,13 +6072,13 @@
         <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>96</v>
+        <v>337</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>75</v>
@@ -6027,10 +6086,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6053,16 +6112,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6112,7 +6171,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6121,13 +6180,13 @@
         <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>96</v>
+        <v>344</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>75</v>
@@ -6135,10 +6194,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6161,16 +6220,16 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6220,7 +6279,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6229,13 +6288,13 @@
         <v>77</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>75</v>
@@ -6243,10 +6302,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6272,13 +6331,13 @@
         <v>232</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6304,13 +6363,13 @@
         <v>75</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -6328,7 +6387,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6337,13 +6396,13 @@
         <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
@@ -6351,10 +6410,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6377,13 +6436,13 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6434,7 +6493,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6443,13 +6502,13 @@
         <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -6457,10 +6516,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6483,13 +6542,13 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6540,7 +6599,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6555,7 +6614,7 @@
         <v>75</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
@@ -6563,14 +6622,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6589,16 +6648,16 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6636,19 +6695,19 @@
         <v>75</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6657,13 +6716,13 @@
         <v>77</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
@@ -6671,14 +6730,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6697,16 +6756,16 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>202</v>
@@ -6758,7 +6817,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6767,13 +6826,13 @@
         <v>77</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>75</v>
@@ -6781,10 +6840,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6810,12 +6869,14 @@
         <v>232</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -6840,10 +6901,10 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="Z48" t="s" s="2">
         <v>75</v>
@@ -6864,7 +6925,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6873,13 +6934,13 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
@@ -6887,10 +6948,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6913,16 +6974,16 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6972,7 +7033,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6981,13 +7042,13 @@
         <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>75</v>
@@ -6995,10 +7056,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7024,13 +7085,13 @@
         <v>232</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7056,13 +7117,13 @@
         <v>75</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -7080,7 +7141,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7089,13 +7150,13 @@
         <v>77</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>75</v>
@@ -7103,10 +7164,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7132,13 +7193,13 @@
         <v>232</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7168,7 +7229,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -7186,7 +7247,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7195,13 +7256,13 @@
         <v>77</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>75</v>
@@ -7209,10 +7270,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7238,13 +7299,13 @@
         <v>232</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7270,13 +7331,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7294,7 +7355,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7303,13 +7364,13 @@
         <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>75</v>
+        <v>393</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>75</v>
@@ -7317,10 +7378,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7346,12 +7407,14 @@
         <v>232</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>75</v>
@@ -7376,13 +7439,13 @@
         <v>75</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -7400,7 +7463,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7409,13 +7472,13 @@
         <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>75</v>
@@ -7423,10 +7486,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7449,13 +7512,13 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7506,7 +7569,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7515,13 +7578,13 @@
         <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>75</v>
@@ -7529,10 +7592,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7555,16 +7618,16 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7614,7 +7677,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7623,13 +7686,13 @@
         <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>75</v>
@@ -7637,10 +7700,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7663,13 +7726,13 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7720,7 +7783,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7735,7 +7798,7 @@
         <v>75</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>75</v>
@@ -7743,14 +7806,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7769,16 +7832,16 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7816,19 +7879,19 @@
         <v>75</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7837,13 +7900,13 @@
         <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>75</v>
@@ -7851,14 +7914,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7877,16 +7940,16 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>202</v>
@@ -7938,7 +8001,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7947,13 +8010,13 @@
         <v>77</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>75</v>
@@ -7961,10 +8024,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7987,15 +8050,17 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>75</v>
@@ -8023,10 +8088,10 @@
         <v>225</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -8044,7 +8109,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8053,13 +8118,13 @@
         <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>75</v>
@@ -8067,10 +8132,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8093,13 +8158,13 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8150,7 +8215,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8159,13 +8224,13 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>75</v>
@@ -8173,10 +8238,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8199,16 +8264,16 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8258,7 +8323,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8267,13 +8332,13 @@
         <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8281,10 +8346,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8307,16 +8372,16 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8366,7 +8431,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8375,13 +8440,13 @@
         <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>75</v>
@@ -8389,10 +8454,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8415,13 +8480,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8472,7 +8537,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8481,13 +8546,13 @@
         <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>75</v>
@@ -8495,10 +8560,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8521,13 +8586,13 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8578,7 +8643,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8593,7 +8658,7 @@
         <v>75</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>75</v>
@@ -8601,14 +8666,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8627,16 +8692,16 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8674,19 +8739,19 @@
         <v>75</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8695,13 +8760,13 @@
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>75</v>
@@ -8709,14 +8774,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -8735,16 +8800,16 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>202</v>
@@ -8796,7 +8861,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -8805,13 +8870,13 @@
         <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>75</v>
@@ -8819,10 +8884,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8845,15 +8910,17 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>75</v>
@@ -8902,7 +8969,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>84</v>
@@ -8911,13 +8978,13 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>75</v>
@@ -8925,10 +8992,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8954,12 +9021,14 @@
         <v>260</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>75</v>
@@ -9008,7 +9077,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9017,13 +9086,13 @@
         <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>96</v>
+        <v>265</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>75</v>
@@ -9031,10 +9100,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9057,15 +9126,17 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -9114,7 +9185,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9123,13 +9194,13 @@
         <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>75</v>
@@ -9137,10 +9208,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9163,15 +9234,17 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -9220,7 +9293,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9229,13 +9302,13 @@
         <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>102</v>
+        <v>445</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="434">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>act[classCode=ACT][moodCode=DEF]</t>
@@ -310,334 +310,334 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace</t>
+  </si>
+  <si>
+    <t>as-ext-data-trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
+</t>
+  </si>
+  <si>
+    <t>DataTrace : Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI).</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>HealthcareService.implicitRules</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>HealthcareService.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>HealthcareService.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>HealthcareService.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-healthcareservice-authorization</t>
+  </si>
+  <si>
+    <t>as-ext-healthcareservice-authorization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization}
+</t>
+  </si>
+  <si>
+    <t>AS HealthcareService Autorization Extension</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les autorisations  des activités sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels lourds autorisés.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.extension:as-ext-data-trace</t>
-  </si>
-  <si>
-    <t>as-ext-data-trace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
-</t>
-  </si>
-  <si>
-    <t>DataTrace : Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI).</t>
-  </si>
-  <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>HealthcareService.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>HealthcareService.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>HealthcareService.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>HealthcareService.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization</t>
-  </si>
-  <si>
-    <t>as-ext-healthcareservice-authorization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization}
-</t>
-  </si>
-  <si>
-    <t>AS HealthcareService Autorization Extension</t>
-  </si>
-  <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les autorisations  des activités sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels lourds autorisés.</t>
-  </si>
-  <si>
     <t>HealthcareService.modifierExtension</t>
   </si>
   <si>
@@ -835,15 +835,7 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
     <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
@@ -871,10 +863,6 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
   </si>
   <si>
@@ -959,9 +947,6 @@
   </si>
   <si>
     <t>The specific type of service that may be delivered or performed.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J131-CategorieActiviteSanitaireRegulee-RASS/FHIR/JDV-J131-CategorieActiviteSanitaireRegulee-RASS</t>
@@ -997,9 +982,6 @@
     <t>The location(s) where this healthcare service may be provided.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>.location.role[classCode=SDLOC]</t>
   </si>
   <si>
@@ -1013,9 +995,6 @@
   </si>
   <si>
     <t>Further description of the service as it would be presented to a consumer while searching.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>.name</t>
@@ -1049,9 +1028,6 @@
     <t>Extra details about the service that can't be placed in the other fields.</t>
   </si>
   <si>
-    <t>Systems are not required to have markdown support, so the text should be readable without markdown processing. The markdown syntax is GFM - see https://github.github.com/gfm/</t>
-  </si>
-  <si>
     <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].text</t>
   </si>
   <si>
@@ -1068,13 +1044,6 @@
     <t>If there is a photo/symbol associated with this HealthcareService, it may be included here to facilitate quick identification of the service in a list.</t>
   </si>
   <si>
-    <t>When providing a summary view (for example with Observation.value[x]) Attachment should be represented with a brief display text such as "Signed Procedure Consent".</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}</t>
-  </si>
-  <si>
     <t>.actrelationship[typeCode=SBJ].observation.value</t>
   </si>
   <si>
@@ -1094,10 +1063,6 @@
     <t>If this is empty, then refer to the location's contacts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
-  </si>
-  <si>
     <t>.telecom</t>
   </si>
   <si>
@@ -1245,9 +1210,6 @@
     <t>When using this property it indicates that the service is available with this language, it is not derived from the practitioners, and not all are required to use this language, just that this language is available while scheduling.</t>
   </si>
   <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>HealthcareService.referralMethod</t>
   </si>
   <si>
@@ -1401,9 +1363,6 @@
   </si>
   <si>
     <t>Technical endpoints providing access to services operated for the specific healthcare services defined at this resource.</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
 </sst>
 </file>
@@ -2186,13 +2145,13 @@
         <v>84</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK4" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>75</v>
@@ -2200,10 +2159,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2226,13 +2185,13 @@
         <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L5" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2283,7 +2242,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -2298,7 +2257,7 @@
         <v>75</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>75</v>
@@ -2306,14 +2265,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2332,16 +2291,16 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2379,19 +2338,19 @@
         <v>75</v>
       </c>
       <c r="AB6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC6" t="s" s="2">
+      <c r="AF6" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -2400,13 +2359,13 @@
         <v>77</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>75</v>
@@ -2414,13 +2373,13 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>75</v>
@@ -2442,13 +2401,13 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2499,7 +2458,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -2508,10 +2467,10 @@
         <v>77</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
@@ -2522,10 +2481,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2551,13 +2510,13 @@
         <v>86</v>
       </c>
       <c r="L8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2607,7 +2566,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2616,13 +2575,13 @@
         <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ8" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK8" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>75</v>
@@ -2630,10 +2589,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2656,16 +2615,16 @@
         <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2715,7 +2674,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2724,13 +2683,13 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ9" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK9" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>75</v>
@@ -2738,10 +2697,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2764,16 +2723,16 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2823,7 +2782,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2832,13 +2791,13 @@
         <v>84</v>
       </c>
       <c r="AI10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ10" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK10" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>75</v>
@@ -2846,10 +2805,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2872,16 +2831,16 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2931,7 +2890,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -2940,13 +2899,13 @@
         <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK11" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>75</v>
@@ -2954,10 +2913,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2980,16 +2939,16 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3015,31 +2974,31 @@
         <v>75</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="Z12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="AA12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3048,13 +3007,13 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK12" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>75</v>
@@ -3062,10 +3021,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3088,16 +3047,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3123,31 +3082,31 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3156,13 +3115,13 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK13" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>75</v>
@@ -3170,10 +3129,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3196,16 +3155,16 @@
         <v>85</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3255,7 +3214,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3264,13 +3223,13 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK14" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>75</v>
@@ -3278,10 +3237,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3304,16 +3263,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3339,31 +3298,31 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3372,13 +3331,13 @@
         <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK15" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>75</v>
@@ -3386,14 +3345,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3412,16 +3371,16 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3471,7 +3430,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3480,13 +3439,13 @@
         <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK16" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>75</v>
@@ -3494,14 +3453,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3520,16 +3479,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3579,7 +3538,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3594,7 +3553,7 @@
         <v>75</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>75</v>
@@ -3602,14 +3561,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3628,17 +3587,15 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>108</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3675,19 +3632,17 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC18" s="2"/>
+      <c r="AD18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC18" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>113</v>
-      </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3696,13 +3651,13 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>75</v>
@@ -3710,13 +3665,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>75</v>
@@ -3738,13 +3693,13 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3795,7 +3750,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3804,10 +3759,10 @@
         <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>75</v>
@@ -3825,7 +3780,7 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3844,7 +3799,7 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>200</v>
@@ -3853,7 +3808,7 @@
         <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O20" t="s" s="2">
         <v>202</v>
@@ -3893,16 +3848,16 @@
         <v>75</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>203</v>
@@ -3914,13 +3869,13 @@
         <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>75</v>
@@ -4008,7 +3963,7 @@
         <v>75</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>204</v>
@@ -4020,10 +3975,10 @@
         <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>210</v>
@@ -4128,10 +4083,10 @@
         <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>210</v>
@@ -4168,13 +4123,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4225,7 +4180,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4240,7 +4195,7 @@
         <v>75</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>75</v>
@@ -4255,7 +4210,7 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4274,16 +4229,16 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4321,19 +4276,19 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE24" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC24" t="s" s="2">
+      <c r="AF24" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4342,13 +4297,13 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>75</v>
@@ -4382,7 +4337,7 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>221</v>
@@ -4452,10 +4407,10 @@
         <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>229</v>
@@ -4529,7 +4484,7 @@
         <v>75</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Y26" t="s" s="2">
         <v>237</v>
@@ -4562,10 +4517,10 @@
         <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>229</v>
@@ -4602,7 +4557,7 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>242</v>
@@ -4672,10 +4627,10 @@
         <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>249</v>
@@ -4712,7 +4667,7 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>252</v>
@@ -4780,10 +4735,10 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>257</v>
@@ -4828,9 +4783,7 @@
       <c r="M29" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>263</v>
-      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -4879,7 +4832,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4888,13 +4841,13 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>265</v>
-      </c>
       <c r="AK29" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>75</v>
@@ -4902,10 +4855,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4928,16 +4881,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4987,7 +4940,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4996,13 +4949,13 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ30" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AK30" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>75</v>
@@ -5010,10 +4963,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5036,23 +4989,23 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q31" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="R31" t="s" s="2">
         <v>75</v>
@@ -5097,7 +5050,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5106,24 +5059,24 @@
         <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ31" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK31" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5146,16 +5099,16 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5205,7 +5158,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5214,13 +5167,13 @@
         <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ32" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AK32" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>75</v>
@@ -5228,14 +5181,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5257,13 +5210,13 @@
         <v>232</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5293,7 +5246,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>75</v>
@@ -5311,7 +5264,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5320,28 +5273,28 @@
         <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ33" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK33" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5363,14 +5316,12 @@
         <v>232</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5399,7 +5350,7 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5417,7 +5368,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5426,13 +5377,13 @@
         <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK34" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>75</v>
@@ -5440,10 +5391,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5469,14 +5420,12 @@
         <v>232</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5505,7 +5454,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5523,7 +5472,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5532,13 +5481,13 @@
         <v>77</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK35" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>75</v>
@@ -5546,10 +5495,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5572,17 +5521,15 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -5631,7 +5578,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5640,24 +5587,24 @@
         <v>77</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AK36" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5680,17 +5627,15 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -5739,7 +5684,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5748,13 +5693,13 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK37" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>75</v>
@@ -5762,10 +5707,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5788,16 +5733,16 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5847,7 +5792,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5856,13 +5801,13 @@
         <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ38" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK38" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>75</v>
@@ -5870,10 +5815,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5896,17 +5841,15 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -5955,7 +5898,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5964,13 +5907,13 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ39" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK39" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>75</v>
@@ -5978,10 +5921,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6004,17 +5947,15 @@
         <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -6063,7 +6004,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6072,13 +6013,13 @@
         <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ40" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="AK40" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>75</v>
@@ -6086,10 +6027,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6112,16 +6053,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6171,7 +6112,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6180,13 +6121,13 @@
         <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ41" t="s" s="2">
-        <v>344</v>
-      </c>
       <c r="AK41" t="s" s="2">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>75</v>
@@ -6194,10 +6135,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6220,16 +6161,16 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6279,7 +6220,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6288,13 +6229,13 @@
         <v>77</v>
       </c>
       <c r="AI42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ42" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AK42" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>75</v>
@@ -6302,10 +6243,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6331,13 +6272,13 @@
         <v>232</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6363,13 +6304,13 @@
         <v>75</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -6387,7 +6328,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6396,13 +6337,13 @@
         <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ43" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK43" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
@@ -6410,10 +6351,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6436,13 +6377,13 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6493,7 +6434,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6502,13 +6443,13 @@
         <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ44" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK44" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -6516,10 +6457,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6542,13 +6483,13 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6599,7 +6540,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6614,7 +6555,7 @@
         <v>75</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
@@ -6622,14 +6563,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6648,16 +6589,16 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6695,19 +6636,19 @@
         <v>75</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6716,13 +6657,13 @@
         <v>77</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
@@ -6730,14 +6671,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6756,16 +6697,16 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>202</v>
@@ -6817,7 +6758,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6826,13 +6767,13 @@
         <v>77</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>75</v>
@@ -6840,10 +6781,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6869,14 +6810,12 @@
         <v>232</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -6901,10 +6840,10 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="Z48" t="s" s="2">
         <v>75</v>
@@ -6925,7 +6864,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6934,13 +6873,13 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ48" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK48" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
@@ -6948,10 +6887,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6974,16 +6913,16 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7033,7 +6972,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7042,13 +6981,13 @@
         <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ49" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK49" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>75</v>
@@ -7056,10 +6995,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7085,13 +7024,13 @@
         <v>232</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7117,13 +7056,13 @@
         <v>75</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -7141,7 +7080,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7150,13 +7089,13 @@
         <v>77</v>
       </c>
       <c r="AI50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ50" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK50" t="s" s="2">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>75</v>
@@ -7164,10 +7103,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7193,13 +7132,13 @@
         <v>232</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7229,7 +7168,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -7247,7 +7186,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7256,13 +7195,13 @@
         <v>77</v>
       </c>
       <c r="AI51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ51" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK51" t="s" s="2">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>75</v>
@@ -7270,10 +7209,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7299,13 +7238,13 @@
         <v>232</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7331,13 +7270,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7355,7 +7294,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7364,13 +7303,13 @@
         <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ52" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK52" t="s" s="2">
-        <v>393</v>
+        <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>75</v>
@@ -7378,10 +7317,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7407,14 +7346,12 @@
         <v>232</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>75</v>
@@ -7439,13 +7376,13 @@
         <v>75</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -7463,7 +7400,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7472,13 +7409,13 @@
         <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ53" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK53" t="s" s="2">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>75</v>
@@ -7486,10 +7423,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7512,13 +7449,13 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7569,7 +7506,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7578,13 +7515,13 @@
         <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ54" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK54" t="s" s="2">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>75</v>
@@ -7592,10 +7529,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7618,16 +7555,16 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7677,7 +7614,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7686,13 +7623,13 @@
         <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ55" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK55" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>75</v>
@@ -7700,10 +7637,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7726,13 +7663,13 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7783,7 +7720,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7798,7 +7735,7 @@
         <v>75</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>75</v>
@@ -7806,14 +7743,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7832,16 +7769,16 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7879,19 +7816,19 @@
         <v>75</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7900,13 +7837,13 @@
         <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>75</v>
@@ -7914,14 +7851,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7940,16 +7877,16 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>202</v>
@@ -8001,7 +7938,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8010,13 +7947,13 @@
         <v>77</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>75</v>
@@ -8024,10 +7961,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8050,17 +7987,15 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>75</v>
@@ -8088,10 +8023,10 @@
         <v>225</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -8109,7 +8044,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8118,13 +8053,13 @@
         <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ59" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK59" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>75</v>
@@ -8132,10 +8067,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8158,13 +8093,13 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8215,7 +8150,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8224,13 +8159,13 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ60" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK60" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>75</v>
@@ -8238,10 +8173,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8264,16 +8199,16 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8323,7 +8258,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8332,13 +8267,13 @@
         <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ61" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK61" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8346,10 +8281,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8372,16 +8307,16 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8431,7 +8366,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8440,13 +8375,13 @@
         <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ62" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK62" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>75</v>
@@ -8454,10 +8389,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8480,13 +8415,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8537,7 +8472,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8546,13 +8481,13 @@
         <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ63" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK63" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>75</v>
@@ -8560,10 +8495,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8586,13 +8521,13 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8643,7 +8578,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8658,7 +8593,7 @@
         <v>75</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>75</v>
@@ -8666,14 +8601,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8692,16 +8627,16 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8739,19 +8674,19 @@
         <v>75</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8760,13 +8695,13 @@
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>75</v>
@@ -8774,14 +8709,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -8800,16 +8735,16 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>202</v>
@@ -8861,7 +8796,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -8870,13 +8805,13 @@
         <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>75</v>
@@ -8884,10 +8819,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8910,17 +8845,15 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>75</v>
@@ -8969,7 +8902,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>84</v>
@@ -8978,13 +8911,13 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ67" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK67" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>75</v>
@@ -8992,10 +8925,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9021,14 +8954,12 @@
         <v>260</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>75</v>
@@ -9077,7 +9008,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9086,13 +9017,13 @@
         <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ68" t="s" s="2">
-        <v>265</v>
-      </c>
       <c r="AK68" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>75</v>
@@ -9100,10 +9031,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9126,17 +9057,15 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -9185,7 +9114,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9194,13 +9123,13 @@
         <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ69" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK69" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>75</v>
@@ -9208,10 +9137,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9234,17 +9163,15 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -9293,7 +9220,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9302,13 +9229,13 @@
         <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ70" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AK70" t="s" s="2">
-        <v>445</v>
+        <v>102</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="446">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>act[classCode=ACT][moodCode=DEF]</t>
@@ -310,10 +310,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>HealthcareService.meta.id</t>
   </si>
   <si>
@@ -487,6 +494,9 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>HealthcareService.meta.tag</t>
   </si>
   <si>
@@ -603,16 +613,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>HealthcareService.extension</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -634,10 +638,6 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les autorisations  des activités sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels lourds autorisés.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>HealthcareService.modifierExtension</t>
   </si>
   <si>
@@ -835,7 +835,15 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
     <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
@@ -863,6 +871,10 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
   </si>
   <si>
@@ -947,6 +959,9 @@
   </si>
   <si>
     <t>The specific type of service that may be delivered or performed.</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J131-CategorieActiviteSanitaireRegulee-RASS/FHIR/JDV-J131-CategorieActiviteSanitaireRegulee-RASS</t>
@@ -982,6 +997,9 @@
     <t>The location(s) where this healthcare service may be provided.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>.location.role[classCode=SDLOC]</t>
   </si>
   <si>
@@ -995,6 +1013,9 @@
   </si>
   <si>
     <t>Further description of the service as it would be presented to a consumer while searching.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>.name</t>
@@ -1028,6 +1049,9 @@
     <t>Extra details about the service that can't be placed in the other fields.</t>
   </si>
   <si>
+    <t>Systems are not required to have markdown support, so the text should be readable without markdown processing. The markdown syntax is GFM - see https://github.github.com/gfm/</t>
+  </si>
+  <si>
     <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].text</t>
   </si>
   <si>
@@ -1044,6 +1068,13 @@
     <t>If there is a photo/symbol associated with this HealthcareService, it may be included here to facilitate quick identification of the service in a list.</t>
   </si>
   <si>
+    <t>When providing a summary view (for example with Observation.value[x]) Attachment should be represented with a brief display text such as "Signed Procedure Consent".</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}</t>
+  </si>
+  <si>
     <t>.actrelationship[typeCode=SBJ].observation.value</t>
   </si>
   <si>
@@ -1063,6 +1094,10 @@
     <t>If this is empty, then refer to the location's contacts.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
+  </si>
+  <si>
     <t>.telecom</t>
   </si>
   <si>
@@ -1210,6 +1245,9 @@
     <t>When using this property it indicates that the service is available with this language, it is not derived from the practitioners, and not all are required to use this language, just that this language is available while scheduling.</t>
   </si>
   <si>
+    <t>CD</t>
+  </si>
+  <si>
     <t>HealthcareService.referralMethod</t>
   </si>
   <si>
@@ -1363,6 +1401,9 @@
   </si>
   <si>
     <t>Technical endpoints providing access to services operated for the specific healthcare services defined at this resource.</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
 </sst>
 </file>
@@ -2145,13 +2186,13 @@
         <v>84</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>75</v>
@@ -2159,10 +2200,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2185,13 +2226,13 @@
         <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2242,7 +2283,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -2257,7 +2298,7 @@
         <v>75</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>75</v>
@@ -2265,14 +2306,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2291,16 +2332,16 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2338,19 +2379,19 @@
         <v>75</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -2359,13 +2400,13 @@
         <v>77</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>75</v>
@@ -2373,13 +2414,13 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>75</v>
@@ -2401,13 +2442,13 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2458,7 +2499,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -2467,10 +2508,10 @@
         <v>77</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
@@ -2481,10 +2522,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2510,13 +2551,13 @@
         <v>86</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2566,7 +2607,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2575,13 +2616,13 @@
         <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>75</v>
@@ -2589,10 +2630,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2615,16 +2656,16 @@
         <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2674,7 +2715,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2683,13 +2724,13 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>75</v>
@@ -2697,10 +2738,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2723,16 +2764,16 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2782,7 +2823,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2791,13 +2832,13 @@
         <v>84</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>75</v>
@@ -2805,10 +2846,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2831,16 +2872,16 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2890,7 +2931,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -2899,13 +2940,13 @@
         <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>75</v>
@@ -2913,10 +2954,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2939,16 +2980,16 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2974,13 +3015,13 @@
         <v>75</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>75</v>
@@ -2998,7 +3039,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3007,13 +3048,13 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>75</v>
@@ -3021,10 +3062,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3047,16 +3088,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3082,13 +3123,13 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>75</v>
@@ -3106,7 +3147,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3115,13 +3156,13 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>75</v>
@@ -3129,10 +3170,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3155,16 +3196,16 @@
         <v>85</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3214,7 +3255,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3223,13 +3264,13 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>75</v>
@@ -3237,10 +3278,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3263,16 +3304,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3298,13 +3339,13 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>75</v>
@@ -3322,7 +3363,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3331,13 +3372,13 @@
         <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>75</v>
@@ -3345,14 +3386,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3371,16 +3412,16 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3430,7 +3471,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3439,13 +3480,13 @@
         <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>75</v>
@@ -3453,14 +3494,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3479,16 +3520,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3538,7 +3579,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3553,7 +3594,7 @@
         <v>75</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>75</v>
@@ -3561,14 +3602,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3587,15 +3628,17 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>108</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3632,17 +3675,19 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AC18" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3651,13 +3696,13 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>75</v>
@@ -3665,13 +3710,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>75</v>
@@ -3693,13 +3738,13 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3750,7 +3795,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3759,10 +3804,10 @@
         <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>75</v>
@@ -3780,7 +3825,7 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3799,7 +3844,7 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>200</v>
@@ -3808,7 +3853,7 @@
         <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O20" t="s" s="2">
         <v>202</v>
@@ -3848,16 +3893,16 @@
         <v>75</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>203</v>
@@ -3869,13 +3914,13 @@
         <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>75</v>
@@ -3963,7 +4008,7 @@
         <v>75</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>204</v>
@@ -3975,10 +4020,10 @@
         <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>210</v>
@@ -4083,10 +4128,10 @@
         <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>210</v>
@@ -4123,13 +4168,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4180,7 +4225,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4195,7 +4240,7 @@
         <v>75</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>75</v>
@@ -4210,7 +4255,7 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4229,16 +4274,16 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4276,19 +4321,19 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4297,13 +4342,13 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>75</v>
@@ -4337,7 +4382,7 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>221</v>
@@ -4407,10 +4452,10 @@
         <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>229</v>
@@ -4484,7 +4529,7 @@
         <v>75</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y26" t="s" s="2">
         <v>237</v>
@@ -4517,10 +4562,10 @@
         <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>229</v>
@@ -4557,7 +4602,7 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>242</v>
@@ -4627,10 +4672,10 @@
         <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>249</v>
@@ -4667,7 +4712,7 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>252</v>
@@ -4735,10 +4780,10 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>257</v>
@@ -4783,7 +4828,9 @@
       <c r="M29" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="N29" s="2"/>
+      <c r="N29" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -4832,7 +4879,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4841,13 +4888,13 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>96</v>
+        <v>265</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>75</v>
@@ -4855,10 +4902,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4881,16 +4928,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4940,7 +4987,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4949,13 +4996,13 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>75</v>
@@ -4963,10 +5010,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4989,23 +5036,23 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q31" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="R31" t="s" s="2">
         <v>75</v>
@@ -5050,7 +5097,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5059,24 +5106,24 @@
         <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5099,16 +5146,16 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5158,7 +5205,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5167,13 +5214,13 @@
         <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>75</v>
@@ -5181,14 +5228,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5210,13 +5257,13 @@
         <v>232</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5246,7 +5293,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>75</v>
@@ -5264,7 +5311,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5273,28 +5320,28 @@
         <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5316,12 +5363,14 @@
         <v>232</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5350,7 +5399,7 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5368,7 +5417,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5377,13 +5426,13 @@
         <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>75</v>
@@ -5391,10 +5440,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5420,12 +5469,14 @@
         <v>232</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5454,7 +5505,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5472,7 +5523,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5481,13 +5532,13 @@
         <v>77</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>75</v>
@@ -5495,10 +5546,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5521,15 +5572,17 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -5578,7 +5631,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5587,24 +5640,24 @@
         <v>77</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5627,15 +5680,17 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -5684,7 +5739,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5693,13 +5748,13 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>75</v>
@@ -5707,10 +5762,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5733,16 +5788,16 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5792,7 +5847,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5801,13 +5856,13 @@
         <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>75</v>
@@ -5815,10 +5870,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5841,15 +5896,17 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -5898,7 +5955,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5907,13 +5964,13 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>75</v>
@@ -5921,10 +5978,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5947,15 +6004,17 @@
         <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -6004,7 +6063,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6013,13 +6072,13 @@
         <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>96</v>
+        <v>337</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>75</v>
@@ -6027,10 +6086,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6053,16 +6112,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6112,7 +6171,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6121,13 +6180,13 @@
         <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>96</v>
+        <v>344</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>75</v>
@@ -6135,10 +6194,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6161,16 +6220,16 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6220,7 +6279,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6229,13 +6288,13 @@
         <v>77</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>75</v>
@@ -6243,10 +6302,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6272,13 +6331,13 @@
         <v>232</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6304,13 +6363,13 @@
         <v>75</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -6328,7 +6387,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6337,13 +6396,13 @@
         <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
@@ -6351,10 +6410,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6377,13 +6436,13 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6434,7 +6493,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6443,13 +6502,13 @@
         <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -6457,10 +6516,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6483,13 +6542,13 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6540,7 +6599,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6555,7 +6614,7 @@
         <v>75</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
@@ -6563,14 +6622,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6589,16 +6648,16 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6636,19 +6695,19 @@
         <v>75</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6657,13 +6716,13 @@
         <v>77</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
@@ -6671,14 +6730,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6697,16 +6756,16 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>202</v>
@@ -6758,7 +6817,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6767,13 +6826,13 @@
         <v>77</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>75</v>
@@ -6781,10 +6840,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6810,12 +6869,14 @@
         <v>232</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -6840,10 +6901,10 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="Z48" t="s" s="2">
         <v>75</v>
@@ -6864,7 +6925,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6873,13 +6934,13 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
@@ -6887,10 +6948,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6913,16 +6974,16 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6972,7 +7033,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6981,13 +7042,13 @@
         <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>75</v>
@@ -6995,10 +7056,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7024,13 +7085,13 @@
         <v>232</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7056,13 +7117,13 @@
         <v>75</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -7080,7 +7141,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7089,13 +7150,13 @@
         <v>77</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>75</v>
@@ -7103,10 +7164,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7132,13 +7193,13 @@
         <v>232</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7168,7 +7229,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -7186,7 +7247,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7195,13 +7256,13 @@
         <v>77</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>75</v>
@@ -7209,10 +7270,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7238,13 +7299,13 @@
         <v>232</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7270,13 +7331,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7294,7 +7355,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7303,13 +7364,13 @@
         <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>75</v>
+        <v>393</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>75</v>
@@ -7317,10 +7378,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7346,12 +7407,14 @@
         <v>232</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>75</v>
@@ -7376,13 +7439,13 @@
         <v>75</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -7400,7 +7463,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7409,13 +7472,13 @@
         <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>75</v>
@@ -7423,10 +7486,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7449,13 +7512,13 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7506,7 +7569,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7515,13 +7578,13 @@
         <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>75</v>
@@ -7529,10 +7592,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7555,16 +7618,16 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7614,7 +7677,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7623,13 +7686,13 @@
         <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>75</v>
@@ -7637,10 +7700,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7663,13 +7726,13 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7720,7 +7783,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7735,7 +7798,7 @@
         <v>75</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>75</v>
@@ -7743,14 +7806,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7769,16 +7832,16 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7816,19 +7879,19 @@
         <v>75</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7837,13 +7900,13 @@
         <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>75</v>
@@ -7851,14 +7914,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7877,16 +7940,16 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>202</v>
@@ -7938,7 +8001,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7947,13 +8010,13 @@
         <v>77</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>75</v>
@@ -7961,10 +8024,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7987,15 +8050,17 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>75</v>
@@ -8023,10 +8088,10 @@
         <v>225</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -8044,7 +8109,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8053,13 +8118,13 @@
         <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>75</v>
@@ -8067,10 +8132,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8093,13 +8158,13 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8150,7 +8215,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8159,13 +8224,13 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>75</v>
@@ -8173,10 +8238,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8199,16 +8264,16 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8258,7 +8323,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8267,13 +8332,13 @@
         <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8281,10 +8346,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8307,16 +8372,16 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8366,7 +8431,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8375,13 +8440,13 @@
         <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>75</v>
@@ -8389,10 +8454,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8415,13 +8480,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8472,7 +8537,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8481,13 +8546,13 @@
         <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>75</v>
@@ -8495,10 +8560,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8521,13 +8586,13 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8578,7 +8643,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8593,7 +8658,7 @@
         <v>75</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>75</v>
@@ -8601,14 +8666,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8627,16 +8692,16 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8674,19 +8739,19 @@
         <v>75</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8695,13 +8760,13 @@
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>75</v>
@@ -8709,14 +8774,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -8735,16 +8800,16 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>202</v>
@@ -8796,7 +8861,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -8805,13 +8870,13 @@
         <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>75</v>
@@ -8819,10 +8884,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8845,15 +8910,17 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>75</v>
@@ -8902,7 +8969,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>84</v>
@@ -8911,13 +8978,13 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>75</v>
@@ -8925,10 +8992,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8954,12 +9021,14 @@
         <v>260</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>75</v>
@@ -9008,7 +9077,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9017,13 +9086,13 @@
         <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>96</v>
+        <v>265</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>75</v>
@@ -9031,10 +9100,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9057,15 +9126,17 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -9114,7 +9185,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9123,13 +9194,13 @@
         <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>75</v>
@@ -9137,10 +9208,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9163,15 +9234,17 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -9220,7 +9293,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9229,13 +9302,13 @@
         <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>102</v>
+        <v>445</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -622,20 +622,20 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization</t>
-  </si>
-  <si>
-    <t>as-ext-healthcareservice-authorization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization}
+    <t>HealthcareService.extension:as-ext-authorization</t>
+  </si>
+  <si>
+    <t>as-ext-authorization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization}
 </t>
   </si>
   <si>
-    <t>AS HealthcareService Autorization Extension</t>
-  </si>
-  <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les autorisations  des activités sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels lourds autorisés.</t>
+    <t>AS Authorization Extension</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les autorisations des activités (HealthcareService) sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels (Device) lourds autorisés.</t>
   </si>
   <si>
     <t>HealthcareService.modifierExtension</t>
@@ -1723,9 +1723,9 @@
   <dimension ref="A1:AL70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="63.55078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.46484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="49.1328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="36.5703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.67578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0-snapshot</t>
+    <t>1.1.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:20:03+00:00</t>
+    <t>2024-07-11T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T15:24:25+00:00</t>
+    <t>2025-03-18T14:02:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:01:00+00:00</t>
+    <t>2026-06-19T13:53:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -443,7 +443,7 @@
     <t>as-ext-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -751,7 +751,7 @@
     <t>HealthcareService.providedBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -443,7 +443,7 @@
     <t>as-ext-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -751,7 +751,7 @@
     <t>HealthcareService.providedBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-3)
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
